--- a/thejoinery/thejoinery_5_upgraded_products.xlsx
+++ b/thejoinery/thejoinery_5_upgraded_products.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,6 +160,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,35 +571,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Current Word Count</t>
+          <t>Feed Word Count (Shopify API)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Live Storefront Words (Theme)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Diagnostic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Upgraded Description (Clean Readable Text + Specs)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Current Alt Text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Image Alt Text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Google Shopping Category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Smart Tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Live Product URL</t>
         </is>
@@ -628,7 +639,15 @@
       <c r="E2" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>The HIDEAWAY - JOINERY BOOKCASE by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -640,27 +659,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginThejoinery (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>HIDEAWAY - JOINERY BOOKCASE - Thejoinery Official Product View</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>https://thejoinery.com/products/hideaway-joinery-bookcase</t>
         </is>
@@ -690,7 +709,15 @@
       <c r="E3" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>The Hideaway - Corbett 4-Drawer Dresser by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -702,27 +729,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginThejoinery (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Hideaway - Corbett 4-Drawer Dresser - Thejoinery Official Product View</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>https://thejoinery.com/products/hideaway-corbett-4-drawer-dresser</t>
         </is>
@@ -752,7 +779,15 @@
       <c r="E4" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>The Alameda Coffee Table by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -764,27 +799,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginThejoinery (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Alameda Coffee Table - Thejoinery Official Product View</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>https://thejoinery.com/products/mws_apo_1_g2_alameda-coffee-table</t>
         </is>
@@ -814,7 +849,15 @@
       <c r="E5" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Standard Catalog Item</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>The Olive Spoon by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -826,27 +869,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginThejoinery (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Olive Spoon - Thejoinery Official Product View</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>https://thejoinery.com/products/olive-spoon</t>
         </is>
@@ -876,7 +919,15 @@
       <c r="E6" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Standard Catalog Item</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>The Coffee Scoop by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -888,27 +939,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginThejoinery (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Coffee Scoop - Thejoinery Official Product View</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>https://thejoinery.com/products/coffee-scoop</t>
         </is>
@@ -967,164 +1018,164 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Body (HTML)</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Option1 Name</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Option1 Value</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Variant SKU</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Variant Grams</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Tracker</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Qty</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Policy</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Variant Fulfillment Service</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>Variant Price</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>Variant Compare At Price</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>Variant Requires Shipping</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>Variant Taxable</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>Variant Barcode</t>
         </is>
       </c>
-      <c r="V1" s="10" t="inlineStr">
+      <c r="V1" s="11" t="inlineStr">
         <is>
           <t>Image Src</t>
         </is>
       </c>
-      <c r="W1" s="10" t="inlineStr">
+      <c r="W1" s="11" t="inlineStr">
         <is>
           <t>Image Position</t>
         </is>
       </c>
-      <c r="X1" s="10" t="inlineStr">
+      <c r="X1" s="11" t="inlineStr">
         <is>
           <t>Image Alt Text</t>
         </is>
       </c>
-      <c r="Y1" s="10" t="inlineStr">
+      <c r="Y1" s="11" t="inlineStr">
         <is>
           <t>Gift Card</t>
         </is>
       </c>
-      <c r="Z1" s="10" t="inlineStr">
+      <c r="Z1" s="11" t="inlineStr">
         <is>
           <t>SEO Title</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AA1" s="11" t="inlineStr">
         <is>
           <t>SEO Description</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AB1" s="11" t="inlineStr">
         <is>
           <t>Google Shopping / Google Product Category</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AC1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>hideaway-joinery-bookcase</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>HIDEAWAY - JOINERY BOOKCASE | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;HIDEAWAY - JOINERY BOOKCASE&lt;/strong&gt; by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1139,141 +1190,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Thejoinery</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>HIDEAWAY-JOINERY-BOO-FIXED</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>2380.00</t>
         </is>
       </c>
-      <c r="R2" s="11" t="inlineStr"/>
-      <c r="S2" s="11" t="inlineStr">
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T2" s="11" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U2" s="11" t="inlineStr"/>
-      <c r="V2" s="11" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr"/>
+      <c r="V2" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0712/5286/9408/files/Joinery-Bookcase.jpg?v=1764805166</t>
         </is>
       </c>
-      <c r="W2" s="11" t="inlineStr">
+      <c r="W2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X2" s="11" t="inlineStr">
+      <c r="X2" s="12" t="inlineStr">
         <is>
           <t>HIDEAWAY - JOINERY BOOKCASE - Thejoinery Official Product View</t>
         </is>
       </c>
-      <c r="Y2" s="11" t="inlineStr">
+      <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z2" s="11" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
         <is>
           <t>HIDEAWAY - JOINERY BOOKCASE | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA2" s="11" t="inlineStr">
+      <c r="AA2" s="12" t="inlineStr">
         <is>
           <t>The  HIDEAWAY - JOINERY BOOKCASE  by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered</t>
         </is>
       </c>
-      <c r="AB2" s="11" t="inlineStr">
+      <c r="AB2" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="AC2" s="11" t="inlineStr">
+      <c r="AC2" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>hideaway-corbett-4-drawer-dresser</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Hideaway - Corbett 4-Drawer Dresser | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Hideaway - Corbett 4-Drawer Dresser&lt;/strong&gt; by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1288,141 +1339,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Thejoinery</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>HIDEAWAY-CORBETT-4-D-FIXED</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>4212.00</t>
         </is>
       </c>
-      <c r="R3" s="11" t="inlineStr"/>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="11" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr"/>
-      <c r="V3" s="11" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr"/>
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0712/5286/9408/files/DR7C4_CORBETT4DRAWER.jpg?v=1761767935</t>
         </is>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X3" s="11" t="inlineStr">
+      <c r="X3" s="12" t="inlineStr">
         <is>
           <t>Hideaway - Corbett 4-Drawer Dresser - Thejoinery Official Product View</t>
         </is>
       </c>
-      <c r="Y3" s="11" t="inlineStr">
+      <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z3" s="11" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
         <is>
           <t>Hideaway - Corbett 4-Drawer Dresser | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA3" s="11" t="inlineStr">
+      <c r="AA3" s="12" t="inlineStr">
         <is>
           <t>The  Hideaway - Corbett 4-Drawer Dresser  by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully en</t>
         </is>
       </c>
-      <c r="AB3" s="11" t="inlineStr">
+      <c r="AB3" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="AC3" s="11" t="inlineStr">
+      <c r="AC3" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>mws_apo_1_g2_alameda-coffee-table</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Alameda Coffee Table | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Alameda Coffee Table&lt;/strong&gt; by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1437,141 +1488,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Thejoinery</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>MWS_APO_1_G2_ALAMEDA-FIXED</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>4320.00</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0712/5286/9408/files/CT7A_ALAMEDA-COFFEE-TABLE_EASTERN-WALNUT_INDIGO-BLUE-TILE_VIGNETTE.jpg?v=1778731472</t>
         </is>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X4" s="11" t="inlineStr">
+      <c r="X4" s="12" t="inlineStr">
         <is>
           <t>Alameda Coffee Table - Thejoinery Official Product View</t>
         </is>
       </c>
-      <c r="Y4" s="11" t="inlineStr">
+      <c r="Y4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
         <is>
           <t>Alameda Coffee Table | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA4" s="11" t="inlineStr">
+      <c r="AA4" s="12" t="inlineStr">
         <is>
           <t>The  Alameda Coffee Table  by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eli</t>
         </is>
       </c>
-      <c r="AB4" s="11" t="inlineStr">
+      <c r="AB4" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="AC4" s="11" t="inlineStr">
+      <c r="AC4" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>olive-spoon</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Olive Spoon | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Olive Spoon&lt;/strong&gt; by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1586,141 +1637,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Thejoinery</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>OLIVE-SPOON-FIXED</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>24.00</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="11" t="inlineStr">
+      <c r="U5" s="12" t="inlineStr"/>
+      <c r="V5" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0712/5286/9408/files/Olive-spoon.jpg?v=1780517534</t>
         </is>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" s="11" t="inlineStr">
+      <c r="X5" s="12" t="inlineStr">
         <is>
           <t>Olive Spoon - Thejoinery Official Product View</t>
         </is>
       </c>
-      <c r="Y5" s="11" t="inlineStr">
+      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z5" s="11" t="inlineStr">
+      <c r="Z5" s="12" t="inlineStr">
         <is>
           <t>Olive Spoon | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA5" s="11" t="inlineStr">
+      <c r="AA5" s="12" t="inlineStr">
         <is>
           <t>The  Olive Spoon  by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate co</t>
         </is>
       </c>
-      <c r="AB5" s="11" t="inlineStr">
+      <c r="AB5" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="AC5" s="11" t="inlineStr">
+      <c r="AC5" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>coffee-scoop</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Coffee Scoop | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Coffee Scoop&lt;/strong&gt; by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1735,124 +1786,124 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Thejoinery</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>COFFEE-SCOOP-FIXED</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
+      <c r="T6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr">
+      <c r="U6" s="12" t="inlineStr"/>
+      <c r="V6" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0712/5286/9408/files/coffee-scoop.jpg?v=1780517342</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X6" s="11" t="inlineStr">
+      <c r="X6" s="12" t="inlineStr">
         <is>
           <t>Coffee Scoop - Thejoinery Official Product View</t>
         </is>
       </c>
-      <c r="Y6" s="11" t="inlineStr">
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z6" s="11" t="inlineStr">
+      <c r="Z6" s="12" t="inlineStr">
         <is>
           <t>Coffee Scoop | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA6" s="11" t="inlineStr">
+      <c r="AA6" s="12" t="inlineStr">
         <is>
           <t>The  Coffee Scoop  by Thejoinery represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate c</t>
         </is>
       </c>
-      <c r="AB6" s="11" t="inlineStr">
+      <c r="AB6" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="AC6" s="11" t="inlineStr">
+      <c r="AC6" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
